--- a/data/CDPR_Revenue_Analysis.xlsx
+++ b/data/CDPR_Revenue_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tosie\Desktop\projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9695D8-8552-4811-AFEA-6CB8ACC7CC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC8E00B-878C-4407-BF60-0E6C8C5FDA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1110" windowWidth="29040" windowHeight="17520" xr2:uid="{8D18EEC2-743B-47E3-8CD0-9B3567279D3C}"/>
   </bookViews>
@@ -601,51 +601,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -666,6 +621,51 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -792,7 +792,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFA52733-78C7-4C87-BE96-2903797ABA1D}" type="CELLRANGE">
+                    <a:fld id="{63EA8072-7D7E-4CA6-99D6-BBD62C6B6DA0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -825,7 +825,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CDAA1080-DFB3-45F7-B06C-BFFECFC2B39D}" type="CELLRANGE">
+                    <a:fld id="{49FB80AB-2495-4BB2-A2D3-C4B109D633F0}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -869,7 +869,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{106F4277-F7E2-48EB-8E48-B58D402E9713}" type="CELLRANGE">
+                    <a:fld id="{EB50AABD-241A-423B-A50D-2EF7AAB72B55}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -888,7 +888,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -933,7 +932,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7E253321-6AAC-4435-96D8-E77E9D707F8D}" type="CELLRANGE">
+                    <a:fld id="{3942E31F-F419-43A6-86DF-93C27F8E0C6D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -967,7 +966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A08B42C3-E151-4E94-BB41-3A174D5BD99F}" type="CELLRANGE">
+                    <a:fld id="{DC610178-C22A-41E5-83EE-58261043C8E6}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -986,7 +985,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1001,7 +999,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F38B6346-34DE-4AB1-9F27-A7F5316233F7}" type="CELLRANGE">
+                    <a:fld id="{E1A3474D-8090-462B-816C-96CC7003F23E}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1020,7 +1018,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1045,7 +1042,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{922AB1DD-B378-4E27-BF51-B0151C7D36AD}" type="CELLRANGE">
+                    <a:fld id="{238420A7-2E32-4A5F-8BA0-6FBA6EA1611B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1079,7 +1076,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AECE8C09-C2EF-432B-8989-7DD7EB1A5A4F}" type="CELLRANGE">
+                    <a:fld id="{76F6E833-65F1-4D85-BC50-2F1015471A05}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1098,7 +1095,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1113,7 +1109,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{28B84DC3-5351-46AE-9971-344B2FB1BBC3}" type="CELLRANGE">
+                    <a:fld id="{0E32BF52-AAEF-4046-879F-80BACDA24216}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1132,7 +1128,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1147,7 +1142,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{350F1807-9141-40D9-B394-D960E0BC98B8}" type="CELLRANGE">
+                    <a:fld id="{A5E3B66C-E14B-4A2D-AB46-E9CDBF282E6B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1166,7 +1161,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1181,7 +1175,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3C766E92-36AA-4A64-8FEE-10ED8B0FEF67}" type="CELLRANGE">
+                    <a:fld id="{B73353F4-98E2-42DB-8C52-12A74D8820EA}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1748,7 +1742,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AB7F53D2-78C4-4B6F-84BF-DF1AE60B3765}" type="CELLRANGE">
+                    <a:fld id="{51D5796D-F929-469E-8D8B-6AE26996E080}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1781,7 +1775,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C72F2F14-5C69-46AC-9E05-10F417F12F55}" type="CELLRANGE">
+                    <a:fld id="{710F34AF-D1FB-44A0-B56E-285F31811EA6}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1815,7 +1809,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A7B9C603-CCD0-4BF9-BA04-A5DB8E182EA6}" type="CELLRANGE">
+                    <a:fld id="{F3F0F009-9972-4884-A5D8-253E0F31FFDC}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1834,7 +1828,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1864,7 +1857,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{AE7DD490-C744-4ADF-B3B3-B9A779857C35}" type="CELLRANGE">
+                    <a:fld id="{1BC4BEB7-6946-4DFD-AD48-66E2DD9FDB7B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr>
                         <a:defRPr sz="1100" b="1">
@@ -1946,7 +1939,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CDD93E00-8441-494D-B5A8-77CC48854FD8}" type="CELLRANGE">
+                    <a:fld id="{2F63BD57-502F-47B7-88BD-EEF7F870BD1B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1965,7 +1958,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1980,7 +1972,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A48818EC-E4BB-4B60-9542-8C5A94A87AE6}" type="CELLRANGE">
+                    <a:fld id="{050AC119-0C8E-4600-AB55-5C25612BFAF7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2014,7 +2006,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37B38BE4-8469-4F35-95F8-F14AD739EEE3}" type="CELLRANGE">
+                    <a:fld id="{7C291251-1F26-4657-9A94-482C44ADF1D6}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2033,7 +2025,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2048,7 +2039,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9F0FAC5C-8232-417B-B375-CF0012AB19CC}" type="CELLRANGE">
+                    <a:fld id="{15DF823B-7253-4F7F-9CFE-9B5579721F76}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2067,7 +2058,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2082,7 +2072,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{95983A72-0FDF-4FB3-B52B-30E53D0F8800}" type="CELLRANGE">
+                    <a:fld id="{397BDEDD-E14D-4A56-9FA2-24E576D50AE0}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2101,7 +2091,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2116,7 +2105,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{05A9D5F5-CFBC-48BA-90AE-593CCCA0266D}" type="CELLRANGE">
+                    <a:fld id="{749AAAB2-15DC-421F-BDA8-E51C1CB95CA5}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2150,7 +2139,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{21822C79-70E7-4DC0-BEF9-8BF40E8DB457}" type="CELLRANGE">
+                    <a:fld id="{946937F8-2DD4-4769-A514-AD4CDB26E39F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2169,7 +2158,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2184,7 +2172,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A05060E5-006D-4B28-8501-C8F9789F0B5D}" type="CELLRANGE">
+                    <a:fld id="{0926CC41-D923-49EC-88AD-D22A0B8214B3}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2203,7 +2191,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -6034,19 +6021,19 @@
   <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="40" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="40" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" style="40" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="40" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="40" customWidth="1"/>
-    <col min="7" max="7" width="11" style="40" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" style="40" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="40" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="6.42578125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="25" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="25" customWidth="1"/>
+    <col min="7" max="7" width="11" style="25" customWidth="1"/>
+    <col min="8" max="8" width="40.42578125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="25" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="40" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6072,11 +6059,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>2014</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="24" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="13" t="s">
@@ -6085,18 +6072,18 @@
       <c r="D2" s="3">
         <v>4801</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="29">
+      <c r="E2" s="26"/>
+      <c r="F2" s="33">
         <v>21513</v>
       </c>
-      <c r="G2" s="35"/>
+      <c r="G2" s="42"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>2014</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="24" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -6105,16 +6092,19 @@
       <c r="D3" s="3">
         <v>7565</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="36"/>
+      <c r="E3" s="26">
+        <f>(D3-D2)/D2</f>
+        <v>0.57571339304311597</v>
+      </c>
+      <c r="F3" s="34"/>
+      <c r="G3" s="43"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>2014</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="24" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -6123,16 +6113,19 @@
       <c r="D4" s="3">
         <v>2775</v>
       </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="36"/>
+      <c r="E4" s="26">
+        <f t="shared" ref="E4:E45" si="0">(D4-D3)/D3</f>
+        <v>-0.63317911434236618</v>
+      </c>
+      <c r="F4" s="34"/>
+      <c r="G4" s="43"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>2014</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="24" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="13" t="s">
@@ -6141,12 +6134,15 @@
       <c r="D5" s="3">
         <v>6372</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="37"/>
+      <c r="E5" s="26">
+        <f t="shared" si="0"/>
+        <v>1.2962162162162163</v>
+      </c>
+      <c r="F5" s="35"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>2015</v>
       </c>
@@ -6159,18 +6155,19 @@
       <c r="D6" s="8">
         <v>2857</v>
       </c>
-      <c r="E6" s="41">
-        <v>-0.40491564257446366</v>
-      </c>
-      <c r="F6" s="29">
+      <c r="E6" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.5516321406151915</v>
+      </c>
+      <c r="F6" s="33">
         <v>630856</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <v>28.324408497187747</v>
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2015</v>
       </c>
@@ -6183,16 +6180,17 @@
       <c r="D7" s="3">
         <v>406248</v>
       </c>
-      <c r="E7" s="41">
-        <v>52.700991407799073</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="33"/>
+      <c r="E7" s="26">
+        <f t="shared" si="0"/>
+        <v>141.19390969548476</v>
+      </c>
+      <c r="F7" s="34"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>2015</v>
       </c>
@@ -6205,14 +6203,15 @@
       <c r="D8" s="3">
         <v>85022</v>
       </c>
-      <c r="E8" s="41">
-        <v>29.638558558558557</v>
-      </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="33"/>
+      <c r="E8" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.79071404659222932</v>
+      </c>
+      <c r="F8" s="34"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2015</v>
       </c>
@@ -6225,16 +6224,17 @@
       <c r="D9" s="3">
         <v>136729</v>
       </c>
-      <c r="E9" s="41">
-        <v>20.457784055241682</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="34"/>
+      <c r="E9" s="26">
+        <f t="shared" si="0"/>
+        <v>0.60816024087883136</v>
+      </c>
+      <c r="F9" s="35"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>2016</v>
       </c>
@@ -6247,18 +6247,19 @@
       <c r="D10" s="3">
         <v>63667</v>
       </c>
-      <c r="E10" s="41">
-        <v>21.284564228211412</v>
-      </c>
-      <c r="F10" s="29">
+      <c r="E10" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.53435628140335989</v>
+      </c>
+      <c r="F10" s="33">
         <v>438763</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="30">
         <v>-0.30449579618803657</v>
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2016</v>
       </c>
@@ -6271,16 +6272,17 @@
       <c r="D11" s="3">
         <v>175537</v>
       </c>
-      <c r="E11" s="41">
-        <v>-0.56790679584884107</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="33"/>
+      <c r="E11" s="26">
+        <f t="shared" si="0"/>
+        <v>1.7571112193129879</v>
+      </c>
+      <c r="F11" s="34"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>2016</v>
       </c>
@@ -6293,14 +6295,15 @@
       <c r="D12" s="3">
         <v>72418</v>
       </c>
-      <c r="E12" s="41">
-        <v>-0.14824398391004681</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="33"/>
+      <c r="E12" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.58744879996809785</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>2016</v>
       </c>
@@ -6313,16 +6316,17 @@
       <c r="D13" s="3">
         <v>127141</v>
       </c>
-      <c r="E13" s="41">
-        <v>-7.0124114123558276E-2</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="34"/>
+      <c r="E13" s="26">
+        <f t="shared" si="0"/>
+        <v>0.75565467149051346</v>
+      </c>
+      <c r="F13" s="35"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>2017</v>
       </c>
@@ -6335,18 +6339,19 @@
       <c r="D14" s="3">
         <v>77710</v>
       </c>
-      <c r="E14" s="41">
-        <v>0.22056952581400097</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="E14" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.38878882500530909</v>
+      </c>
+      <c r="F14" s="33">
         <v>346841</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <v>-0.2095026244236638</v>
       </c>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>2017</v>
       </c>
@@ -6359,14 +6364,15 @@
       <c r="D15" s="3">
         <v>121911</v>
       </c>
-      <c r="E15" s="41">
-        <v>-0.30549684681861944</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="33"/>
+      <c r="E15" s="26">
+        <f t="shared" si="0"/>
+        <v>0.56879423497619352</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="31"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>2017</v>
       </c>
@@ -6379,14 +6385,15 @@
       <c r="D16" s="3">
         <v>59087</v>
       </c>
-      <c r="E16" s="41">
-        <v>-0.18408406749703113</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="33"/>
+      <c r="E16" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.51532675476372103</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>2017</v>
       </c>
@@ -6399,16 +6406,17 @@
       <c r="D17" s="3">
         <v>88133</v>
       </c>
-      <c r="E17" s="41">
-        <v>-0.30680897586144518</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="34"/>
+      <c r="E17" s="26">
+        <f t="shared" si="0"/>
+        <v>0.49158021222942438</v>
+      </c>
+      <c r="F17" s="35"/>
+      <c r="G17" s="32"/>
       <c r="H17" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>2018</v>
       </c>
@@ -6421,18 +6429,19 @@
       <c r="D18" s="3">
         <v>52217</v>
       </c>
-      <c r="E18" s="41">
-        <v>-0.32805301762964867</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="E18" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.40752045204406978</v>
+      </c>
+      <c r="F18" s="33">
         <v>235919</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="30">
         <v>-0.31980648193264349</v>
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>2018</v>
       </c>
@@ -6445,14 +6454,15 @@
       <c r="D19" s="3">
         <v>56555</v>
       </c>
-      <c r="E19" s="41">
-        <v>-0.53609600446227168</v>
-      </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="33"/>
+      <c r="E19" s="26">
+        <f t="shared" si="0"/>
+        <v>8.3076392745657548E-2</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>2018</v>
       </c>
@@ -6465,14 +6475,15 @@
       <c r="D20" s="3">
         <v>40675</v>
       </c>
-      <c r="E20" s="41">
-        <v>-0.31160830639565384</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="33"/>
+      <c r="E20" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.28078861285474316</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>2018</v>
       </c>
@@ -6485,14 +6496,15 @@
       <c r="D21" s="3">
         <v>86472</v>
       </c>
-      <c r="E21" s="41">
-        <v>-1.8846516060953333E-2</v>
-      </c>
-      <c r="F21" s="31"/>
-      <c r="G21" s="34"/>
+      <c r="E21" s="26">
+        <f t="shared" si="0"/>
+        <v>1.1259250153657037</v>
+      </c>
+      <c r="F21" s="35"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>2019</v>
       </c>
@@ -6505,18 +6517,19 @@
       <c r="D22" s="3">
         <v>50870</v>
       </c>
-      <c r="E22" s="41">
-        <v>-2.579619664094069E-2</v>
-      </c>
-      <c r="F22" s="29">
+      <c r="E22" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.41171708761217501</v>
+      </c>
+      <c r="F22" s="33">
         <v>304475</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="30">
         <v>0.2905912622552656</v>
       </c>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>2019</v>
       </c>
@@ -6529,16 +6542,17 @@
       <c r="D23" s="3">
         <v>58905</v>
       </c>
-      <c r="E23" s="41">
-        <v>4.155247104588454E-2</v>
-      </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="33"/>
+      <c r="E23" s="26">
+        <f t="shared" si="0"/>
+        <v>0.15795164143896206</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="31"/>
       <c r="H23" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>2019</v>
       </c>
@@ -6551,14 +6565,15 @@
       <c r="D24" s="3">
         <v>47147</v>
       </c>
-      <c r="E24" s="41">
-        <v>0.15911493546404426</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="33"/>
+      <c r="E24" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.19960954078601137</v>
+      </c>
+      <c r="F24" s="34"/>
+      <c r="G24" s="31"/>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2019</v>
       </c>
@@ -6571,14 +6586,15 @@
       <c r="D25" s="3">
         <v>147553</v>
       </c>
-      <c r="E25" s="41">
-        <v>0.70636737903598856</v>
-      </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="34"/>
+      <c r="E25" s="26">
+        <f t="shared" si="0"/>
+        <v>2.1296370924979322</v>
+      </c>
+      <c r="F25" s="35"/>
+      <c r="G25" s="32"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>2020</v>
       </c>
@@ -6591,20 +6607,21 @@
       <c r="D26" s="3">
         <v>137220</v>
       </c>
-      <c r="E26" s="41">
-        <v>1.6974641242382544</v>
-      </c>
-      <c r="F26" s="29">
+      <c r="E26" s="26">
+        <f t="shared" si="0"/>
+        <v>-7.0029074298726554E-2</v>
+      </c>
+      <c r="F26" s="33">
         <v>1839932</v>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="30">
         <v>5.0429657607356928</v>
       </c>
       <c r="H26" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>2020</v>
       </c>
@@ -6617,16 +6634,17 @@
       <c r="D27" s="3">
         <v>100445</v>
       </c>
-      <c r="E27" s="41">
-        <v>0.70520329343858756</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="33"/>
+      <c r="E27" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.26800029150269639</v>
+      </c>
+      <c r="F27" s="34"/>
+      <c r="G27" s="31"/>
       <c r="H27" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>2020</v>
       </c>
@@ -6639,16 +6657,17 @@
       <c r="D28" s="3">
         <v>61902</v>
       </c>
-      <c r="E28" s="41">
-        <v>0.31295734617260906</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="33"/>
+      <c r="E28" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.38372243516352234</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="31"/>
       <c r="H28" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>2020</v>
       </c>
@@ -6661,16 +6680,17 @@
       <c r="D29" s="4">
         <v>1540365</v>
       </c>
-      <c r="E29" s="41">
-        <v>9.4394014354164266</v>
-      </c>
-      <c r="F29" s="31"/>
-      <c r="G29" s="34"/>
+      <c r="E29" s="26">
+        <f t="shared" si="0"/>
+        <v>23.883929436851798</v>
+      </c>
+      <c r="F29" s="35"/>
+      <c r="G29" s="32"/>
       <c r="H29" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>2021</v>
       </c>
@@ -6683,18 +6703,19 @@
       <c r="D30" s="4">
         <v>145868</v>
       </c>
-      <c r="E30" s="41">
-        <v>6.3022882961667401E-2</v>
-      </c>
-      <c r="F30" s="29">
+      <c r="E30" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.90530296390790499</v>
+      </c>
+      <c r="F30" s="33">
         <v>691564</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="30">
         <v>-0.62413610937795527</v>
       </c>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>2021</v>
       </c>
@@ -6707,16 +6728,17 @@
       <c r="D31" s="4">
         <v>221118</v>
       </c>
-      <c r="E31" s="41">
-        <v>1.2013838419035292</v>
-      </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="33"/>
+      <c r="E31" s="26">
+        <f t="shared" si="0"/>
+        <v>0.51587736857981192</v>
+      </c>
+      <c r="F31" s="34"/>
+      <c r="G31" s="31"/>
       <c r="H31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>2021</v>
       </c>
@@ -6729,16 +6751,17 @@
       <c r="D32" s="4">
         <v>104262</v>
       </c>
-      <c r="E32" s="41">
-        <v>0.68430745371716584</v>
-      </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="33"/>
+      <c r="E32" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.52847800721786553</v>
+      </c>
+      <c r="F32" s="34"/>
+      <c r="G32" s="31"/>
       <c r="H32" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>2021</v>
       </c>
@@ -6751,14 +6774,15 @@
       <c r="D33" s="4">
         <v>220316</v>
       </c>
-      <c r="E33" s="41">
-        <v>-0.85697156193499591</v>
-      </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="34"/>
+      <c r="E33" s="26">
+        <f t="shared" si="0"/>
+        <v>1.1130996911626478</v>
+      </c>
+      <c r="F33" s="35"/>
+      <c r="G33" s="32"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>2022</v>
       </c>
@@ -6771,20 +6795,21 @@
       <c r="D34" s="4">
         <v>173787</v>
       </c>
-      <c r="E34" s="41">
-        <v>0.19139907313461485</v>
-      </c>
-      <c r="F34" s="29">
+      <c r="E34" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.21119210588427531</v>
+      </c>
+      <c r="F34" s="33">
         <v>767499</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="30">
         <v>0.10980184046595833</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>2022</v>
       </c>
@@ -6797,16 +6822,17 @@
       <c r="D35" s="4">
         <v>112081</v>
       </c>
-      <c r="E35" s="41">
-        <v>-0.49311679736611219</v>
-      </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="33"/>
+      <c r="E35" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.35506683468844047</v>
+      </c>
+      <c r="F35" s="34"/>
+      <c r="G35" s="31"/>
       <c r="H35" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>2022</v>
       </c>
@@ -6819,16 +6845,17 @@
       <c r="D36" s="4">
         <v>203189</v>
       </c>
-      <c r="E36" s="41">
-        <v>0.94883083002436175</v>
-      </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="33"/>
+      <c r="E36" s="26">
+        <f t="shared" si="0"/>
+        <v>0.81287640188792032</v>
+      </c>
+      <c r="F36" s="34"/>
+      <c r="G36" s="31"/>
       <c r="H36" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>2022</v>
       </c>
@@ -6841,16 +6868,17 @@
       <c r="D37" s="4">
         <v>278442</v>
       </c>
-      <c r="E37" s="41">
-        <v>0.26383013489714774</v>
-      </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="34"/>
+      <c r="E37" s="26">
+        <f t="shared" si="0"/>
+        <v>0.37035961592409039</v>
+      </c>
+      <c r="F37" s="35"/>
+      <c r="G37" s="32"/>
       <c r="H37" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>2023</v>
       </c>
@@ -6863,18 +6891,19 @@
       <c r="D38" s="4">
         <v>130595</v>
       </c>
-      <c r="E38" s="41">
-        <v>-0.24853412510717143</v>
-      </c>
-      <c r="F38" s="29">
+      <c r="E38" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.53097952176754948</v>
+      </c>
+      <c r="F38" s="33">
         <v>1041784</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="30">
         <v>0.35737505846913153</v>
       </c>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>2023</v>
       </c>
@@ -6887,14 +6916,15 @@
       <c r="D39" s="4">
         <v>107489</v>
       </c>
-      <c r="E39" s="41">
-        <v>-4.0970369643382909E-2</v>
-      </c>
-      <c r="F39" s="30"/>
-      <c r="G39" s="33"/>
+      <c r="E39" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.17692867261380604</v>
+      </c>
+      <c r="F39" s="34"/>
+      <c r="G39" s="31"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>2023</v>
       </c>
@@ -6907,16 +6937,17 @@
       <c r="D40" s="4">
         <v>390534</v>
       </c>
-      <c r="E40" s="41">
-        <v>0.92202333787754254</v>
-      </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="33"/>
+      <c r="E40" s="26">
+        <f t="shared" si="0"/>
+        <v>2.6332461926336648</v>
+      </c>
+      <c r="F40" s="34"/>
+      <c r="G40" s="31"/>
       <c r="H40" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>2023</v>
       </c>
@@ -6929,16 +6960,17 @@
       <c r="D41" s="4">
         <v>413166</v>
       </c>
-      <c r="E41" s="41">
-        <v>0.48384941926864483</v>
-      </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="34"/>
+      <c r="E41" s="26">
+        <f t="shared" si="0"/>
+        <v>5.7951420362887737E-2</v>
+      </c>
+      <c r="F41" s="35"/>
+      <c r="G41" s="32"/>
       <c r="H41" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>2024</v>
       </c>
@@ -6951,18 +6983,19 @@
       <c r="D42" s="4">
         <v>185591</v>
       </c>
-      <c r="E42" s="41">
-        <v>0.42111872583176996</v>
-      </c>
-      <c r="F42" s="29">
+      <c r="E42" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.55080766568401074</v>
+      </c>
+      <c r="F42" s="33">
         <v>797396</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="30">
         <v>-0.23458605622662662</v>
       </c>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>2024</v>
       </c>
@@ -6975,14 +7008,15 @@
       <c r="D43" s="4">
         <v>157238</v>
       </c>
-      <c r="E43" s="41">
-        <v>0.46282875457023509</v>
-      </c>
-      <c r="F43" s="30"/>
-      <c r="G43" s="33"/>
+      <c r="E43" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.15277141671740549</v>
+      </c>
+      <c r="F43" s="34"/>
+      <c r="G43" s="31"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>2024</v>
       </c>
@@ -6995,18 +7029,19 @@
       <c r="D44" s="4">
         <v>180158</v>
       </c>
-      <c r="E44" s="41">
-        <v>-0.53868805276877296</v>
-      </c>
-      <c r="F44" s="30"/>
-      <c r="G44" s="33"/>
+      <c r="E44" s="26">
+        <f t="shared" si="0"/>
+        <v>0.14576629059133289</v>
+      </c>
+      <c r="F44" s="34"/>
+      <c r="G44" s="31"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>2024</v>
       </c>
-      <c r="B45" s="39" t="s">
+      <c r="B45" s="24" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="13" t="s">
@@ -7015,21 +7050,22 @@
       <c r="D45" s="3">
         <v>274409</v>
       </c>
-      <c r="E45" s="41">
-        <v>-0.33583837973114922</v>
-      </c>
-      <c r="F45" s="31"/>
-      <c r="G45" s="34"/>
+      <c r="E45" s="26">
+        <f t="shared" si="0"/>
+        <v>0.523157450682179</v>
+      </c>
+      <c r="F45" s="35"/>
+      <c r="G45" s="32"/>
       <c r="H45" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>2025</v>
       </c>
@@ -7042,18 +7078,18 @@
       <c r="D48" s="12">
         <v>179832</v>
       </c>
-      <c r="E48" s="42">
+      <c r="E48" s="27">
         <v>-3.1030599544158929E-2</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="36">
         <v>724803.4475924049</v>
       </c>
-      <c r="G48" s="26">
+      <c r="G48" s="39">
         <v>-9.1037015996562679E-2</v>
       </c>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21">
         <v>2025</v>
       </c>
@@ -7066,14 +7102,14 @@
       <c r="D49" s="18">
         <v>215752.12872392911</v>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="28">
         <v>0.3610494961878527</v>
       </c>
-      <c r="F49" s="24"/>
-      <c r="G49" s="27"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="40"/>
       <c r="H49" s="16"/>
     </row>
-    <row r="50" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21">
         <v>2025</v>
       </c>
@@ -7086,14 +7122,14 @@
       <c r="D50" s="18">
         <v>121531.06890325664</v>
       </c>
-      <c r="E50" s="43">
+      <c r="E50" s="28">
         <v>0.36100002675542653</v>
       </c>
-      <c r="F50" s="24"/>
-      <c r="G50" s="27"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="40"/>
       <c r="H50" s="16"/>
     </row>
-    <row r="51" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21">
         <v>2025</v>
       </c>
@@ -7106,15 +7142,15 @@
       <c r="D51" s="18">
         <v>207688.24996521923</v>
       </c>
-      <c r="E51" s="43">
+      <c r="E51" s="28">
         <v>-0.18170719056843873</v>
       </c>
-      <c r="F51" s="25"/>
-      <c r="G51" s="28"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="41"/>
       <c r="H51" s="19"/>
     </row>
-    <row r="52" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="44">
+    <row r="52" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="29">
         <v>2026</v>
       </c>
       <c r="B52" s="16" t="s">
@@ -7126,19 +7162,19 @@
       <c r="D52" s="18">
         <v>148430.38993153075</v>
       </c>
-      <c r="E52" s="43">
+      <c r="E52" s="28">
         <v>0.21185592994506547</v>
       </c>
-      <c r="F52" s="23">
+      <c r="F52" s="36">
         <v>653194.66418511141</v>
       </c>
-      <c r="G52" s="26">
+      <c r="G52" s="39">
         <v>-9.8797520410751238E-2</v>
       </c>
       <c r="H52" s="16"/>
     </row>
-    <row r="53" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="44">
+    <row r="53" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="29">
         <v>2026</v>
       </c>
       <c r="B53" s="16" t="s">
@@ -7150,15 +7186,15 @@
       <c r="D53" s="18">
         <v>198087.63740002186</v>
       </c>
-      <c r="E53" s="43">
+      <c r="E53" s="28">
         <v>-7.5556123975874731E-2</v>
       </c>
-      <c r="F53" s="24"/>
-      <c r="G53" s="27"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="40"/>
       <c r="H53" s="16"/>
     </row>
-    <row r="54" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="44">
+    <row r="54" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="29">
         <v>2026</v>
       </c>
       <c r="B54" s="16" t="s">
@@ -7170,15 +7206,15 @@
       <c r="D54" s="18">
         <v>122713.79697460329</v>
       </c>
-      <c r="E54" s="43">
+      <c r="E54" s="28">
         <v>-0.21318964151211378</v>
       </c>
-      <c r="F54" s="24"/>
-      <c r="G54" s="27"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="40"/>
       <c r="H54" s="16"/>
     </row>
-    <row r="55" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="44">
+    <row r="55" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="29">
         <v>2026</v>
       </c>
       <c r="B55" s="16" t="s">
@@ -7190,19 +7226,19 @@
       <c r="D55" s="18">
         <v>183962.83987895545</v>
       </c>
-      <c r="E55" s="43">
+      <c r="E55" s="28">
         <v>-4.6530060564736131E-2</v>
       </c>
-      <c r="F55" s="25"/>
-      <c r="G55" s="28"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="41"/>
       <c r="H55" s="16"/>
     </row>
-    <row r="56" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="38" t="s">
+    <row r="56" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21">
         <v>2026</v>
       </c>
@@ -7215,18 +7251,18 @@
       <c r="D57" s="18">
         <v>155665.94480820085</v>
       </c>
-      <c r="E57" s="43">
+      <c r="E57" s="28">
         <v>-0.13438128470905708</v>
       </c>
-      <c r="F57" s="23">
+      <c r="F57" s="36">
         <v>1288316.1379912619</v>
       </c>
-      <c r="G57" s="26">
+      <c r="G57" s="39">
         <v>0.97233108080956543</v>
       </c>
       <c r="H57" s="16"/>
     </row>
-    <row r="58" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21">
         <v>2026</v>
       </c>
@@ -7239,16 +7275,16 @@
       <c r="D58" s="18">
         <v>755745.84061898128</v>
       </c>
-      <c r="E58" s="43">
+      <c r="E58" s="28">
         <v>2.502843031440094</v>
       </c>
-      <c r="F58" s="24"/>
-      <c r="G58" s="27"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="40"/>
       <c r="H58" s="16" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21">
         <v>2026</v>
       </c>
@@ -7261,14 +7297,14 @@
       <c r="D59" s="18">
         <v>139845.525722438</v>
       </c>
-      <c r="E59" s="43">
+      <c r="E59" s="28">
         <v>0.15069773502741254</v>
       </c>
-      <c r="F59" s="24"/>
-      <c r="G59" s="27"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="40"/>
       <c r="H59" s="16"/>
     </row>
-    <row r="60" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21">
         <v>2026</v>
       </c>
@@ -7281,52 +7317,53 @@
       <c r="D60" s="18">
         <v>237058.82684164197</v>
       </c>
-      <c r="E60" s="43">
+      <c r="E60" s="28">
         <v>0.14141665155029867</v>
       </c>
-      <c r="F60" s="25"/>
-      <c r="G60" s="28"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="41"/>
       <c r="H60" s="16"/>
     </row>
-    <row r="61" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G6:G9"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="F18:F21"/>
     <mergeCell ref="G26:G29"/>
     <mergeCell ref="G22:G25"/>
     <mergeCell ref="F22:F25"/>
     <mergeCell ref="F26:F29"/>
     <mergeCell ref="F57:F60"/>
     <mergeCell ref="G57:G60"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="G6:G9"/>
     <mergeCell ref="G38:G41"/>
     <mergeCell ref="G34:G37"/>
     <mergeCell ref="G30:G33"/>
@@ -7337,8 +7374,6 @@
     <mergeCell ref="G48:G51"/>
     <mergeCell ref="F52:F55"/>
     <mergeCell ref="G52:G55"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="G42:G45"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/CDPR_Revenue_Analysis.xlsx
+++ b/data/CDPR_Revenue_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tosie\Desktop\projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC8E00B-878C-4407-BF60-0E6C8C5FDA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34476DE1-16BC-4A27-924D-F743FB2B714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1110" windowWidth="29040" windowHeight="17520" xr2:uid="{8D18EEC2-743B-47E3-8CD0-9B3567279D3C}"/>
   </bookViews>
@@ -48,7 +48,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Przychód 2026 może zbliżyć się do rekordu z 2020
+          <t xml:space="preserve">Revenue 2026 may approach 2020 record
 </t>
         </r>
       </text>
@@ -58,16 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="90">
-  <si>
-    <t>Rok</t>
-  </si>
-  <si>
-    <t>Kwartał</t>
-  </si>
-  <si>
-    <t>Komentarz (np. ważne wydarzenia)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
   <si>
     <t>Q4</t>
   </si>
@@ -87,12 +78,6 @@
     <t>Patch 1.5</t>
   </si>
   <si>
-    <t>Ogłoszenie Phantom Liberty</t>
-  </si>
-  <si>
-    <t>Przedział miesięczny</t>
-  </si>
-  <si>
     <t>01.01.2020-31.03.2020</t>
   </si>
   <si>
@@ -147,15 +132,9 @@
     <t>01.01.2025-31.03.2025</t>
   </si>
   <si>
-    <t>Peak sprzedaży dodatku i Patch 2.1</t>
-  </si>
-  <si>
     <t>Patch 2.2</t>
   </si>
   <si>
-    <t>Suma rocznych przychodów</t>
-  </si>
-  <si>
     <t>01.01.2015-31.03.2015</t>
   </si>
   <si>
@@ -192,45 +171,9 @@
     <t>01.07.2018-30.09.2018</t>
   </si>
   <si>
-    <t>Premiera Wiedźmin 3 Dziki Gon</t>
-  </si>
-  <si>
-    <t>Wersja nextgen na konsole</t>
-  </si>
-  <si>
-    <t>Premiera Cyberpunk 2077</t>
-  </si>
-  <si>
-    <t>Premiera Phantom Liberty i Patch 2.0</t>
-  </si>
-  <si>
-    <t>Start przedsprzedaży CP2077</t>
-  </si>
-  <si>
     <t>Patch 1.3</t>
   </si>
   <si>
-    <t>1 opóźnienie</t>
-  </si>
-  <si>
-    <t>2 opóźnienie</t>
-  </si>
-  <si>
-    <t>3 opóźnienie</t>
-  </si>
-  <si>
-    <t>Premiera Serce z Kamienia</t>
-  </si>
-  <si>
-    <t>Premiera Krew i Wino</t>
-  </si>
-  <si>
-    <t>Next‑Gen aktualizacje dla konsol</t>
-  </si>
-  <si>
-    <t>Przychód ze sprzedaży produktów (tyś. zł)</t>
-  </si>
-  <si>
     <t>Game of the Year Edition</t>
   </si>
   <si>
@@ -249,12 +192,6 @@
     <t>01.07.2026-30.09.2026</t>
   </si>
   <si>
-    <t>Wzrost QoQ</t>
-  </si>
-  <si>
-    <t>Wzrost YoY</t>
-  </si>
-  <si>
     <t>01.01.2014-31.03.2014</t>
   </si>
   <si>
@@ -306,28 +243,88 @@
     <t>01.10.2019-30.12.2019</t>
   </si>
   <si>
-    <t>Premiera nowego dodatku</t>
-  </si>
-  <si>
     <t>Edgerunners</t>
   </si>
   <si>
-    <t>Prognoza może różnić się w zależności od:</t>
-  </si>
-  <si>
-    <t>Terminu premiery DLC,</t>
-  </si>
-  <si>
-    <t>Jakości dodatku (metacritic),</t>
-  </si>
-  <si>
-    <t>Kondycji rynku gamingowego w 2026.</t>
-  </si>
-  <si>
-    <t>Prognoza spekulacyjna (z wyjątkiem Q1 2025) na podstawie danych historycznych z 2023-2025. Uwzględniono średni wzrost sezonowy (Q4 +20%). Scenariusz z dodatkiem zakłada wzrost o 263% w Q2 2026 (na podstawie efektu Phantom Liberty).</t>
-  </si>
-  <si>
-    <t>Prognoza z DLC</t>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Monthly range</t>
+  </si>
+  <si>
+    <t>QoQ growth</t>
+  </si>
+  <si>
+    <t>Total annual revenue</t>
+  </si>
+  <si>
+    <t>YoY growth</t>
+  </si>
+  <si>
+    <t>Revenue from product sales (thousand PLN)</t>
+  </si>
+  <si>
+    <t>Comment (e.g., important events)</t>
+  </si>
+  <si>
+    <t>The Witcher 3 premiere</t>
+  </si>
+  <si>
+    <t>Heart of Stone premiere</t>
+  </si>
+  <si>
+    <t>Blood and Wine premiere</t>
+  </si>
+  <si>
+    <t>Next‑Gen update for consoles</t>
+  </si>
+  <si>
+    <t>Start of CP2077 pre-sales</t>
+  </si>
+  <si>
+    <t>First delay</t>
+  </si>
+  <si>
+    <t>Second delay</t>
+  </si>
+  <si>
+    <t>Third delay</t>
+  </si>
+  <si>
+    <t>Cyberpunk 2077 premiere</t>
+  </si>
+  <si>
+    <t>Announcement Phantom Liberty</t>
+  </si>
+  <si>
+    <t>Phantom Liberty premiere and Patch 2.0</t>
+  </si>
+  <si>
+    <t>Peak sales of the DLC and Patch 2.1</t>
+  </si>
+  <si>
+    <t>Premiere of new DLC</t>
+  </si>
+  <si>
+    <t>Speculative forecast (except Q1 2025) based on historical data from 2023-2025. Seasonal average growth (Q4 +20%) is included. Scenario with addition assumes 263% growth in Q2 2026 (based on Phantom Liberty effect).</t>
+  </si>
+  <si>
+    <t>Forecast with DLC</t>
+  </si>
+  <si>
+    <t>The forecast may vary depending on:</t>
+  </si>
+  <si>
+    <t>DLC release date,</t>
+  </si>
+  <si>
+    <t>DLC quality (metacritic),</t>
+  </si>
+  <si>
+    <t>The condition of the gaming market in 2026.</t>
   </si>
 </sst>
 </file>
@@ -640,6 +637,15 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -656,15 +662,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -728,7 +725,7 @@
                 </a:solidFill>
                 <a:latin typeface="Rajdhani" panose="02000000000000000000" pitchFamily="2" charset="-18"/>
               </a:rPr>
-              <a:t>Przychód kWARTALNY PO WYDANIU CP2077</a:t>
+              <a:t>QUARTERLY REVENUE AFTER CP2077 RELEASE</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -792,7 +789,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{63EA8072-7D7E-4CA6-99D6-BBD62C6B6DA0}" type="CELLRANGE">
+                    <a:fld id="{02F97794-1A38-4263-8B35-10EF4550562A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -825,7 +822,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{49FB80AB-2495-4BB2-A2D3-C4B109D633F0}" type="CELLRANGE">
+                    <a:fld id="{AC24FB69-D22F-4BAB-B9DE-7278FFA965B7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -869,7 +866,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EB50AABD-241A-423B-A50D-2EF7AAB72B55}" type="CELLRANGE">
+                    <a:fld id="{CAB0A438-39BA-4B44-9DEE-E3BF12733334}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -888,6 +885,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -932,7 +930,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3942E31F-F419-43A6-86DF-93C27F8E0C6D}" type="CELLRANGE">
+                    <a:fld id="{2C9F55C6-99CA-4F5D-90D7-4F6EA1D2E28E}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -966,83 +964,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC610178-C22A-41E5-83EE-58261043C8E6}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
-                      <a:pPr/>
-                      <a:t>[ZAKRES KOMÓREK]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-GB"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-619B-4034-AA38-D94D21FDA9D5}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{E1A3474D-8090-462B-816C-96CC7003F23E}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
-                      <a:pPr/>
-                      <a:t>[ZAKRES KOMÓREK]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-GB"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-619B-4034-AA38-D94D21FDA9D5}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:delete val="1"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-619B-4034-AA38-D94D21FDA9D5}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{238420A7-2E32-4A5F-8BA0-6FBA6EA1611B}" type="CELLRANGE">
+                    <a:fld id="{14D95C14-36CC-4F5E-ABA0-81939D4A1DBC}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1065,18 +987,18 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-619B-4034-AA38-D94D21FDA9D5}"/>
+                  <c16:uniqueId val="{00000009-619B-4034-AA38-D94D21FDA9D5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="12"/>
+              <c:idx val="9"/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{76F6E833-65F1-4D85-BC50-2F1015471A05}" type="CELLRANGE">
+                    <a:fld id="{8B77BD92-0D90-445C-9FE9-11FA71819032}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1095,21 +1017,67 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-619B-4034-AA38-D94D21FDA9D5}"/>
+                  <c16:uniqueId val="{0000000A-619B-4034-AA38-D94D21FDA9D5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="13"/>
+              <c:idx val="10"/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0E32BF52-AAEF-4046-879F-80BACDA24216}" type="CELLRANGE">
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>Phantom</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t> Liberty premiere and Patch 2.0</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-619B-4034-AA38-D94D21FDA9D5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-619B-4034-AA38-D94D21FDA9D5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A185950D-E25C-4F9E-A888-AF5631594C30}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1128,21 +1096,22 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-619B-4034-AA38-D94D21FDA9D5}"/>
+                  <c16:uniqueId val="{0000000C-619B-4034-AA38-D94D21FDA9D5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="14"/>
+              <c:idx val="13"/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5E3B66C-E14B-4A2D-AB46-E9CDBF282E6B}" type="CELLRANGE">
+                    <a:fld id="{1C9518BA-0E75-47F7-984B-9B1FF60233A8}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1161,6 +1130,41 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-619B-4034-AA38-D94D21FDA9D5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{9E15197D-6BEC-4E7C-AAAE-5A3FA7819BAA}" type="CELLRANGE">
+                      <a:rPr lang="en-GB"/>
+                      <a:pPr/>
+                      <a:t>[ZAKRES KOMÓREK]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-GB"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1175,7 +1179,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B73353F4-98E2-42DB-8C52-12A74D8820EA}" type="CELLRANGE">
+                    <a:fld id="{DB8B504E-9B7E-4DA4-9785-A849448C73B9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1464,22 +1468,22 @@
                     <c:v>Patch 1.3</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Wersja nextgen na konsole</c:v>
+                    <c:v>Next‑Gen update for consoles</c:v>
                   </c:pt>
                   <c:pt idx="5">
                     <c:v>Patch 1.5</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Ogłoszenie Phantom Liberty</c:v>
+                    <c:v>Announcement Phantom Liberty</c:v>
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>Edgerunners</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Premiera Phantom Liberty i Patch 2.0</c:v>
+                    <c:v>Phantom Liberty premiere and Patch 2.0</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Peak sprzedaży dodatku i Patch 2.1</c:v>
+                    <c:v>Peak sales of the DLC and Patch 2.1</c:v>
                   </c:pt>
                   <c:pt idx="15">
                     <c:v>Patch 2.2</c:v>
@@ -1679,7 +1683,7 @@
                 </a:solidFill>
                 <a:latin typeface="D-DIN Condensed" panose="020B0506030202030204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>PRZYCHÓD KWARTALNY PO WYDANIU WITCHER 3</a:t>
+              <a:t>QUARTERLY REVENUE AFTER WITCHER 3 RELEASE</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1742,7 +1746,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51D5796D-F929-469E-8D8B-6AE26996E080}" type="CELLRANGE">
+                    <a:fld id="{3E13E4A7-D81C-41CC-94B2-A61197D31D3B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1775,7 +1779,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{710F34AF-D1FB-44A0-B56E-285F31811EA6}" type="CELLRANGE">
+                    <a:fld id="{4A3B80CA-B0C0-4C5E-81C1-9A4A6A341DFA}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1809,7 +1813,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F3F0F009-9972-4884-A5D8-253E0F31FFDC}" type="CELLRANGE">
+                    <a:fld id="{586C87E8-706A-42CA-859C-0008A8EB7951}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1857,7 +1861,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{1BC4BEB7-6946-4DFD-AD48-66E2DD9FDB7B}" type="CELLRANGE">
+                    <a:fld id="{4A64C9D0-F4A9-4D06-BB60-1EC2DBE23699}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr>
                         <a:defRPr sz="1100" b="1">
@@ -1939,7 +1943,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F63BD57-502F-47B7-88BD-EEF7F870BD1B}" type="CELLRANGE">
+                    <a:fld id="{EAAD7C44-5BEE-4166-AD1E-DDB94433D9E6}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1972,7 +1976,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{050AC119-0C8E-4600-AB55-5C25612BFAF7}" type="CELLRANGE">
+                    <a:fld id="{23A31C7B-6E20-4B3B-AFB4-C20CA87F7648}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2006,7 +2010,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C291251-1F26-4657-9A94-482C44ADF1D6}" type="CELLRANGE">
+                    <a:fld id="{3E0125E4-5914-4935-9245-B3889EAA1F1F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2039,7 +2043,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{15DF823B-7253-4F7F-9CFE-9B5579721F76}" type="CELLRANGE">
+                    <a:fld id="{A0873FC1-CFD4-4241-9E3D-DC9FF163E87D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2072,7 +2076,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{397BDEDD-E14D-4A56-9FA2-24E576D50AE0}" type="CELLRANGE">
+                    <a:fld id="{5264B0B2-BDB6-47A8-80D7-A1025DD9F9DD}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2105,7 +2109,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{749AAAB2-15DC-421F-BDA8-E51C1CB95CA5}" type="CELLRANGE">
+                    <a:fld id="{394AC151-9642-44EB-A7B8-A1243ED0BEB9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2139,7 +2143,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{946937F8-2DD4-4769-A514-AD4CDB26E39F}" type="CELLRANGE">
+                    <a:fld id="{414632CC-45EC-40C8-9A40-5B87446B6F69}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2172,7 +2176,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0926CC41-D923-49EC-88AD-D22A0B8214B3}" type="CELLRANGE">
+                    <a:fld id="{3051B2E5-B9D9-4A73-A7EA-3A1414D58D64}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2416,16 +2420,16 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="12"/>
                   <c:pt idx="1">
-                    <c:v>Premiera Serce z Kamienia</c:v>
+                    <c:v>Heart of Stone premiere</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Premiera Krew i Wino</c:v>
+                    <c:v>Blood and Wine premiere</c:v>
                   </c:pt>
                   <c:pt idx="5">
                     <c:v>Game of the Year Edition</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Next‑Gen aktualizacje dla konsol</c:v>
+                    <c:v>Next‑Gen update for consoles</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -2635,11 +2639,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pl-PL"/>
-              <a:t>Prognoza bez wydania</a:t>
+              <a:t>Forecast without the release of the new</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="pl-PL" baseline="0"/>
-              <a:t> dodatku</a:t>
+              <a:t> DLC</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB"/>
           </a:p>
@@ -3002,11 +3006,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pl-PL"/>
-              <a:t>Prognoza po wydaniu</a:t>
+              <a:t>Forecast after the release of the</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="pl-PL" baseline="0"/>
-              <a:t> dodatku</a:t>
+              <a:t> new DLC</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB"/>
           </a:p>
@@ -3016,8 +3020,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.26868744531933508"/>
-          <c:y val="2.7777777777777776E-2"/>
+          <c:x val="0.21751564462173262"/>
+          <c:y val="2.7777892294982932E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -6023,8 +6027,8 @@
   <cols>
     <col min="1" max="1" width="6.42578125" style="25" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" style="25" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="25" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" style="25" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" style="25" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" style="25" customWidth="1"/>
     <col min="7" max="7" width="11" style="25" customWidth="1"/>
@@ -6035,28 +6039,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6064,10 +6068,10 @@
         <v>2014</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3">
         <v>4801</v>
@@ -6076,7 +6080,7 @@
       <c r="F2" s="33">
         <v>21513</v>
       </c>
-      <c r="G2" s="42"/>
+      <c r="G2" s="36"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6084,10 +6088,10 @@
         <v>2014</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3">
         <v>7565</v>
@@ -6097,7 +6101,7 @@
         <v>0.57571339304311597</v>
       </c>
       <c r="F3" s="34"/>
-      <c r="G3" s="43"/>
+      <c r="G3" s="37"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6105,10 +6109,10 @@
         <v>2014</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3">
         <v>2775</v>
@@ -6118,7 +6122,7 @@
         <v>-0.63317911434236618</v>
       </c>
       <c r="F4" s="34"/>
-      <c r="G4" s="43"/>
+      <c r="G4" s="37"/>
       <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6126,10 +6130,10 @@
         <v>2014</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3">
         <v>6372</v>
@@ -6139,7 +6143,7 @@
         <v>1.2962162162162163</v>
       </c>
       <c r="F5" s="35"/>
-      <c r="G5" s="44"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6147,10 +6151,10 @@
         <v>2015</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D6" s="8">
         <v>2857</v>
@@ -6172,10 +6176,10 @@
         <v>2015</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
         <v>406248</v>
@@ -6187,7 +6191,7 @@
       <c r="F7" s="34"/>
       <c r="G7" s="31"/>
       <c r="H7" s="6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6195,10 +6199,10 @@
         <v>2015</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
         <v>85022</v>
@@ -6216,10 +6220,10 @@
         <v>2015</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D9" s="3">
         <v>136729</v>
@@ -6231,7 +6235,7 @@
       <c r="F9" s="35"/>
       <c r="G9" s="32"/>
       <c r="H9" s="6" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6239,10 +6243,10 @@
         <v>2016</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3">
         <v>63667</v>
@@ -6264,10 +6268,10 @@
         <v>2016</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
         <v>175537</v>
@@ -6279,7 +6283,7 @@
       <c r="F11" s="34"/>
       <c r="G11" s="31"/>
       <c r="H11" s="6" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6287,10 +6291,10 @@
         <v>2016</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3">
         <v>72418</v>
@@ -6308,10 +6312,10 @@
         <v>2016</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3">
         <v>127141</v>
@@ -6323,7 +6327,7 @@
       <c r="F13" s="35"/>
       <c r="G13" s="32"/>
       <c r="H13" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6331,10 +6335,10 @@
         <v>2017</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D14" s="3">
         <v>77710</v>
@@ -6356,10 +6360,10 @@
         <v>2017</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D15" s="3">
         <v>121911</v>
@@ -6377,10 +6381,10 @@
         <v>2017</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3">
         <v>59087</v>
@@ -6398,10 +6402,10 @@
         <v>2017</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3">
         <v>88133</v>
@@ -6413,7 +6417,7 @@
       <c r="F17" s="35"/>
       <c r="G17" s="32"/>
       <c r="H17" s="6" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6421,10 +6425,10 @@
         <v>2018</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D18" s="3">
         <v>52217</v>
@@ -6446,10 +6450,10 @@
         <v>2018</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3">
         <v>56555</v>
@@ -6467,10 +6471,10 @@
         <v>2018</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D20" s="3">
         <v>40675</v>
@@ -6488,10 +6492,10 @@
         <v>2018</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3">
         <v>86472</v>
@@ -6509,10 +6513,10 @@
         <v>2019</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3">
         <v>50870</v>
@@ -6534,10 +6538,10 @@
         <v>2019</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D23" s="3">
         <v>58905</v>
@@ -6549,7 +6553,7 @@
       <c r="F23" s="34"/>
       <c r="G23" s="31"/>
       <c r="H23" s="14" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6557,10 +6561,10 @@
         <v>2019</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D24" s="3">
         <v>47147</v>
@@ -6578,10 +6582,10 @@
         <v>2019</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3">
         <v>147553</v>
@@ -6599,10 +6603,10 @@
         <v>2020</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="3">
         <v>137220</v>
@@ -6618,7 +6622,7 @@
         <v>5.0429657607356928</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6626,10 +6630,10 @@
         <v>2020</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3">
         <v>100445</v>
@@ -6641,7 +6645,7 @@
       <c r="F27" s="34"/>
       <c r="G27" s="31"/>
       <c r="H27" s="6" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6649,10 +6653,10 @@
         <v>2020</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D28" s="3">
         <v>61902</v>
@@ -6664,7 +6668,7 @@
       <c r="F28" s="34"/>
       <c r="G28" s="31"/>
       <c r="H28" s="6" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6672,10 +6676,10 @@
         <v>2020</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D29" s="4">
         <v>1540365</v>
@@ -6687,7 +6691,7 @@
       <c r="F29" s="35"/>
       <c r="G29" s="32"/>
       <c r="H29" s="2" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6695,10 +6699,10 @@
         <v>2021</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D30" s="4">
         <v>145868</v>
@@ -6720,10 +6724,10 @@
         <v>2021</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D31" s="4">
         <v>221118</v>
@@ -6735,7 +6739,7 @@
       <c r="F31" s="34"/>
       <c r="G31" s="31"/>
       <c r="H31" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6743,10 +6747,10 @@
         <v>2021</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D32" s="4">
         <v>104262</v>
@@ -6758,7 +6762,7 @@
       <c r="F32" s="34"/>
       <c r="G32" s="31"/>
       <c r="H32" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6766,10 +6770,10 @@
         <v>2021</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D33" s="4">
         <v>220316</v>
@@ -6787,10 +6791,10 @@
         <v>2022</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D34" s="4">
         <v>173787</v>
@@ -6806,7 +6810,7 @@
         <v>0.10980184046595833</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6814,10 +6818,10 @@
         <v>2022</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D35" s="4">
         <v>112081</v>
@@ -6829,7 +6833,7 @@
       <c r="F35" s="34"/>
       <c r="G35" s="31"/>
       <c r="H35" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6837,10 +6841,10 @@
         <v>2022</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D36" s="4">
         <v>203189</v>
@@ -6852,7 +6856,7 @@
       <c r="F36" s="34"/>
       <c r="G36" s="31"/>
       <c r="H36" s="2" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6860,10 +6864,10 @@
         <v>2022</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D37" s="4">
         <v>278442</v>
@@ -6875,7 +6879,7 @@
       <c r="F37" s="35"/>
       <c r="G37" s="32"/>
       <c r="H37" s="2" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6883,10 +6887,10 @@
         <v>2023</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D38" s="4">
         <v>130595</v>
@@ -6908,10 +6912,10 @@
         <v>2023</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D39" s="4">
         <v>107489</v>
@@ -6929,10 +6933,10 @@
         <v>2023</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D40" s="4">
         <v>390534</v>
@@ -6944,7 +6948,7 @@
       <c r="F40" s="34"/>
       <c r="G40" s="31"/>
       <c r="H40" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6952,10 +6956,10 @@
         <v>2023</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D41" s="4">
         <v>413166</v>
@@ -6967,7 +6971,7 @@
       <c r="F41" s="35"/>
       <c r="G41" s="32"/>
       <c r="H41" s="2" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6975,10 +6979,10 @@
         <v>2024</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D42" s="4">
         <v>185591</v>
@@ -7000,10 +7004,10 @@
         <v>2024</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D43" s="4">
         <v>157238</v>
@@ -7021,10 +7025,10 @@
         <v>2024</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D44" s="4">
         <v>180158</v>
@@ -7042,10 +7046,10 @@
         <v>2024</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D45" s="3">
         <v>274409</v>
@@ -7057,12 +7061,12 @@
       <c r="F45" s="35"/>
       <c r="G45" s="32"/>
       <c r="H45" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7070,10 +7074,10 @@
         <v>2025</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D48" s="12">
         <v>179832</v>
@@ -7081,10 +7085,10 @@
       <c r="E48" s="27">
         <v>-3.1030599544158929E-2</v>
       </c>
-      <c r="F48" s="36">
+      <c r="F48" s="39">
         <v>724803.4475924049</v>
       </c>
-      <c r="G48" s="39">
+      <c r="G48" s="42">
         <v>-9.1037015996562679E-2</v>
       </c>
       <c r="H48" s="5"/>
@@ -7094,10 +7098,10 @@
         <v>2025</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D49" s="18">
         <v>215752.12872392911</v>
@@ -7105,8 +7109,8 @@
       <c r="E49" s="28">
         <v>0.3610494961878527</v>
       </c>
-      <c r="F49" s="37"/>
-      <c r="G49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="43"/>
       <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7114,10 +7118,10 @@
         <v>2025</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D50" s="18">
         <v>121531.06890325664</v>
@@ -7125,8 +7129,8 @@
       <c r="E50" s="28">
         <v>0.36100002675542653</v>
       </c>
-      <c r="F50" s="37"/>
-      <c r="G50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="43"/>
       <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7134,10 +7138,10 @@
         <v>2025</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D51" s="18">
         <v>207688.24996521923</v>
@@ -7145,8 +7149,8 @@
       <c r="E51" s="28">
         <v>-0.18170719056843873</v>
       </c>
-      <c r="F51" s="38"/>
-      <c r="G51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="44"/>
       <c r="H51" s="19"/>
     </row>
     <row r="52" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7154,10 +7158,10 @@
         <v>2026</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D52" s="18">
         <v>148430.38993153075</v>
@@ -7165,10 +7169,10 @@
       <c r="E52" s="28">
         <v>0.21185592994506547</v>
       </c>
-      <c r="F52" s="36">
+      <c r="F52" s="39">
         <v>653194.66418511141</v>
       </c>
-      <c r="G52" s="39">
+      <c r="G52" s="42">
         <v>-9.8797520410751238E-2</v>
       </c>
       <c r="H52" s="16"/>
@@ -7178,10 +7182,10 @@
         <v>2026</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D53" s="18">
         <v>198087.63740002186</v>
@@ -7189,8 +7193,8 @@
       <c r="E53" s="28">
         <v>-7.5556123975874731E-2</v>
       </c>
-      <c r="F53" s="37"/>
-      <c r="G53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="43"/>
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7198,10 +7202,10 @@
         <v>2026</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D54" s="18">
         <v>122713.79697460329</v>
@@ -7209,8 +7213,8 @@
       <c r="E54" s="28">
         <v>-0.21318964151211378</v>
       </c>
-      <c r="F54" s="37"/>
-      <c r="G54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="43"/>
       <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7218,10 +7222,10 @@
         <v>2026</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D55" s="18">
         <v>183962.83987895545</v>
@@ -7229,13 +7233,13 @@
       <c r="E55" s="28">
         <v>-4.6530060564736131E-2</v>
       </c>
-      <c r="F55" s="38"/>
-      <c r="G55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="44"/>
       <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7243,10 +7247,10 @@
         <v>2026</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D57" s="18">
         <v>155665.94480820085</v>
@@ -7254,10 +7258,10 @@
       <c r="E57" s="28">
         <v>-0.13438128470905708</v>
       </c>
-      <c r="F57" s="36">
+      <c r="F57" s="39">
         <v>1288316.1379912619</v>
       </c>
-      <c r="G57" s="39">
+      <c r="G57" s="42">
         <v>0.97233108080956543</v>
       </c>
       <c r="H57" s="16"/>
@@ -7267,10 +7271,10 @@
         <v>2026</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D58" s="18">
         <v>755745.84061898128</v>
@@ -7278,8 +7282,8 @@
       <c r="E58" s="28">
         <v>2.502843031440094</v>
       </c>
-      <c r="F58" s="37"/>
-      <c r="G58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="43"/>
       <c r="H58" s="16" t="s">
         <v>82</v>
       </c>
@@ -7289,10 +7293,10 @@
         <v>2026</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D59" s="18">
         <v>139845.525722438</v>
@@ -7300,8 +7304,8 @@
       <c r="E59" s="28">
         <v>0.15069773502741254</v>
       </c>
-      <c r="F59" s="37"/>
-      <c r="G59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="43"/>
       <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7309,10 +7313,10 @@
         <v>2026</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D60" s="18">
         <v>237058.82684164197</v>
@@ -7320,48 +7324,38 @@
       <c r="E60" s="28">
         <v>0.14141665155029867</v>
       </c>
-      <c r="F60" s="38"/>
-      <c r="G60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="44"/>
       <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="F42:F45"/>
     <mergeCell ref="G42:G45"/>
-    <mergeCell ref="F6:F9"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="G6:G9"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="G26:G29"/>
-    <mergeCell ref="G22:G25"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="F26:F29"/>
     <mergeCell ref="F57:F60"/>
     <mergeCell ref="G57:G60"/>
     <mergeCell ref="G38:G41"/>
@@ -7374,6 +7368,16 @@
     <mergeCell ref="G48:G51"/>
     <mergeCell ref="F52:F55"/>
     <mergeCell ref="G52:G55"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G18:G21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/CDPR_Revenue_Analysis.xlsx
+++ b/data/CDPR_Revenue_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tosie\Desktop\projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34476DE1-16BC-4A27-924D-F743FB2B714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4643F4-0EF1-43F4-9976-A4565A40FB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1110" windowWidth="29040" windowHeight="17520" xr2:uid="{8D18EEC2-743B-47E3-8CD0-9B3567279D3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D18EEC2-743B-47E3-8CD0-9B3567279D3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -619,6 +619,15 @@
     <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -626,15 +635,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -789,7 +789,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{02F97794-1A38-4263-8B35-10EF4550562A}" type="CELLRANGE">
+                    <a:fld id="{CAECAF42-CA58-4D2A-B237-611478A13D51}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -822,7 +822,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC24FB69-D22F-4BAB-B9DE-7278FFA965B7}" type="CELLRANGE">
+                    <a:fld id="{6E908821-A8F4-4089-8CDA-052D23066816}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -885,7 +885,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -930,7 +929,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2C9F55C6-99CA-4F5D-90D7-4F6EA1D2E28E}" type="CELLRANGE">
+                    <a:fld id="{22C5607E-1960-4B7E-9442-59FA7631B6B8}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -983,7 +982,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1017,7 +1015,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1096,7 +1093,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1130,7 +1126,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1164,7 +1159,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1179,7 +1173,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DB8B504E-9B7E-4DA4-9785-A849448C73B9}" type="CELLRANGE">
+                    <a:fld id="{DAE46517-F15E-44D1-B760-0EA68A915B4A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1746,7 +1740,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3E13E4A7-D81C-41CC-94B2-A61197D31D3B}" type="CELLRANGE">
+                    <a:fld id="{5AE93CF7-711A-4E41-A119-C310108652CA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1779,7 +1773,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4A3B80CA-B0C0-4C5E-81C1-9A4A6A341DFA}" type="CELLRANGE">
+                    <a:fld id="{298D9E95-1F7D-42E5-B1D4-EA90E5EB5927}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1861,7 +1855,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{4A64C9D0-F4A9-4D06-BB60-1EC2DBE23699}" type="CELLRANGE">
+                    <a:fld id="{2BA197E6-76CB-4F0B-AF7D-2A80E35DF6C8}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr>
                         <a:defRPr sz="1100" b="1">
@@ -1976,7 +1970,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{23A31C7B-6E20-4B3B-AFB4-C20CA87F7648}" type="CELLRANGE">
+                    <a:fld id="{C8CA119E-0D25-48E0-9579-8D24913E1BE3}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2109,7 +2103,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{394AC151-9642-44EB-A7B8-A1243ED0BEB9}" type="CELLRANGE">
+                    <a:fld id="{E43A1127-276F-4A9F-975E-E1E385A9AF65}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -6077,7 +6071,7 @@
         <v>4801</v>
       </c>
       <c r="E2" s="26"/>
-      <c r="F2" s="33">
+      <c r="F2" s="30">
         <v>21513</v>
       </c>
       <c r="G2" s="36"/>
@@ -6097,10 +6091,9 @@
         <v>7565</v>
       </c>
       <c r="E3" s="26">
-        <f>(D3-D2)/D2</f>
         <v>0.57571339304311597</v>
       </c>
-      <c r="F3" s="34"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="37"/>
       <c r="H3" s="6"/>
     </row>
@@ -6118,10 +6111,9 @@
         <v>2775</v>
       </c>
       <c r="E4" s="26">
-        <f t="shared" ref="E4:E45" si="0">(D4-D3)/D3</f>
         <v>-0.63317911434236618</v>
       </c>
-      <c r="F4" s="34"/>
+      <c r="F4" s="31"/>
       <c r="G4" s="37"/>
       <c r="H4" s="6"/>
     </row>
@@ -6139,10 +6131,9 @@
         <v>6372</v>
       </c>
       <c r="E5" s="26">
-        <f t="shared" si="0"/>
         <v>1.2962162162162163</v>
       </c>
-      <c r="F5" s="35"/>
+      <c r="F5" s="32"/>
       <c r="G5" s="38"/>
       <c r="H5" s="6"/>
     </row>
@@ -6160,14 +6151,13 @@
         <v>2857</v>
       </c>
       <c r="E6" s="26">
-        <f t="shared" si="0"/>
         <v>-0.5516321406151915</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="30">
         <v>630856</v>
       </c>
-      <c r="G6" s="30">
-        <v>28.324408497187747</v>
+      <c r="G6" s="33">
+        <v>28.324408497187701</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -6185,11 +6175,10 @@
         <v>406248</v>
       </c>
       <c r="E7" s="26">
-        <f t="shared" si="0"/>
         <v>141.19390969548476</v>
       </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="6" t="s">
         <v>70</v>
       </c>
@@ -6208,11 +6197,10 @@
         <v>85022</v>
       </c>
       <c r="E8" s="26">
-        <f t="shared" si="0"/>
         <v>-0.79071404659222932</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6229,11 +6217,10 @@
         <v>136729</v>
       </c>
       <c r="E9" s="26">
-        <f t="shared" si="0"/>
         <v>0.60816024087883136</v>
       </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="6" t="s">
         <v>71</v>
       </c>
@@ -6252,13 +6239,12 @@
         <v>63667</v>
       </c>
       <c r="E10" s="26">
-        <f t="shared" si="0"/>
         <v>-0.53435628140335989</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="30">
         <v>438763</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="33">
         <v>-0.30449579618803657</v>
       </c>
       <c r="H10" s="6"/>
@@ -6277,11 +6263,10 @@
         <v>175537</v>
       </c>
       <c r="E11" s="26">
-        <f t="shared" si="0"/>
         <v>1.7571112193129879</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="6" t="s">
         <v>72</v>
       </c>
@@ -6300,11 +6285,10 @@
         <v>72418</v>
       </c>
       <c r="E12" s="26">
-        <f t="shared" si="0"/>
         <v>-0.58744879996809785</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6321,11 +6305,10 @@
         <v>127141</v>
       </c>
       <c r="E13" s="26">
-        <f t="shared" si="0"/>
         <v>0.75565467149051346</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="6" t="s">
         <v>38</v>
       </c>
@@ -6344,13 +6327,12 @@
         <v>77710</v>
       </c>
       <c r="E14" s="26">
-        <f t="shared" si="0"/>
         <v>-0.38878882500530909</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="30">
         <v>346841</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="33">
         <v>-0.2095026244236638</v>
       </c>
       <c r="H14" s="6"/>
@@ -6369,11 +6351,10 @@
         <v>121911</v>
       </c>
       <c r="E15" s="26">
-        <f t="shared" si="0"/>
         <v>0.56879423497619352</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="34"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6390,11 +6371,10 @@
         <v>59087</v>
       </c>
       <c r="E16" s="26">
-        <f t="shared" si="0"/>
         <v>-0.51532675476372103</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6411,11 +6391,10 @@
         <v>88133</v>
       </c>
       <c r="E17" s="26">
-        <f t="shared" si="0"/>
         <v>0.49158021222942438</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="6" t="s">
         <v>73</v>
       </c>
@@ -6434,13 +6413,12 @@
         <v>52217</v>
       </c>
       <c r="E18" s="26">
-        <f t="shared" si="0"/>
         <v>-0.40752045204406978</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="30">
         <v>235919</v>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="33">
         <v>-0.31980648193264349</v>
       </c>
       <c r="H18" s="6"/>
@@ -6459,11 +6437,10 @@
         <v>56555</v>
       </c>
       <c r="E19" s="26">
-        <f t="shared" si="0"/>
         <v>8.3076392745657548E-2</v>
       </c>
-      <c r="F19" s="34"/>
-      <c r="G19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6480,11 +6457,10 @@
         <v>40675</v>
       </c>
       <c r="E20" s="26">
-        <f t="shared" si="0"/>
         <v>-0.28078861285474316</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6501,11 +6477,10 @@
         <v>86472</v>
       </c>
       <c r="E21" s="26">
-        <f t="shared" si="0"/>
         <v>1.1259250153657037</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6522,13 +6497,12 @@
         <v>50870</v>
       </c>
       <c r="E22" s="26">
-        <f t="shared" si="0"/>
         <v>-0.41171708761217501</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="30">
         <v>304475</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="33">
         <v>0.2905912622552656</v>
       </c>
       <c r="H22" s="6"/>
@@ -6547,11 +6521,10 @@
         <v>58905</v>
       </c>
       <c r="E23" s="26">
-        <f t="shared" si="0"/>
         <v>0.15795164143896206</v>
       </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="14" t="s">
         <v>74</v>
       </c>
@@ -6570,11 +6543,10 @@
         <v>47147</v>
       </c>
       <c r="E24" s="26">
-        <f t="shared" si="0"/>
         <v>-0.19960954078601137</v>
       </c>
-      <c r="F24" s="34"/>
-      <c r="G24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6591,11 +6563,10 @@
         <v>147553</v>
       </c>
       <c r="E25" s="26">
-        <f t="shared" si="0"/>
         <v>2.1296370924979322</v>
       </c>
-      <c r="F25" s="35"/>
-      <c r="G25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="35"/>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6612,13 +6583,12 @@
         <v>137220</v>
       </c>
       <c r="E26" s="26">
-        <f t="shared" si="0"/>
         <v>-7.0029074298726554E-2</v>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="30">
         <v>1839932</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="33">
         <v>5.0429657607356928</v>
       </c>
       <c r="H26" s="14" t="s">
@@ -6639,11 +6609,10 @@
         <v>100445</v>
       </c>
       <c r="E27" s="26">
-        <f t="shared" si="0"/>
         <v>-0.26800029150269639</v>
       </c>
-      <c r="F27" s="34"/>
-      <c r="G27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="34"/>
       <c r="H27" s="6" t="s">
         <v>76</v>
       </c>
@@ -6662,11 +6631,10 @@
         <v>61902</v>
       </c>
       <c r="E28" s="26">
-        <f t="shared" si="0"/>
         <v>-0.38372243516352234</v>
       </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="34"/>
       <c r="H28" s="6" t="s">
         <v>77</v>
       </c>
@@ -6685,11 +6653,10 @@
         <v>1540365</v>
       </c>
       <c r="E29" s="26">
-        <f t="shared" si="0"/>
         <v>23.883929436851798</v>
       </c>
-      <c r="F29" s="35"/>
-      <c r="G29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="2" t="s">
         <v>78</v>
       </c>
@@ -6708,13 +6675,12 @@
         <v>145868</v>
       </c>
       <c r="E30" s="26">
-        <f t="shared" si="0"/>
         <v>-0.90530296390790499</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="30">
         <v>691564</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="33">
         <v>-0.62413610937795527</v>
       </c>
       <c r="H30" s="2"/>
@@ -6733,11 +6699,10 @@
         <v>221118</v>
       </c>
       <c r="E31" s="26">
-        <f t="shared" si="0"/>
         <v>0.51587736857981192</v>
       </c>
-      <c r="F31" s="34"/>
-      <c r="G31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="2" t="s">
         <v>3</v>
       </c>
@@ -6756,11 +6721,10 @@
         <v>104262</v>
       </c>
       <c r="E32" s="26">
-        <f t="shared" si="0"/>
         <v>-0.52847800721786553</v>
       </c>
-      <c r="F32" s="34"/>
-      <c r="G32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="2" t="s">
         <v>37</v>
       </c>
@@ -6779,11 +6743,10 @@
         <v>220316</v>
       </c>
       <c r="E33" s="26">
-        <f t="shared" si="0"/>
         <v>1.1130996911626478</v>
       </c>
-      <c r="F33" s="35"/>
-      <c r="G33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6800,13 +6763,12 @@
         <v>173787</v>
       </c>
       <c r="E34" s="26">
-        <f t="shared" si="0"/>
         <v>-0.21119210588427531</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="30">
         <v>767499</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="33">
         <v>0.10980184046595833</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -6827,11 +6789,10 @@
         <v>112081</v>
       </c>
       <c r="E35" s="26">
-        <f t="shared" si="0"/>
         <v>-0.35506683468844047</v>
       </c>
-      <c r="F35" s="34"/>
-      <c r="G35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="2" t="s">
         <v>5</v>
       </c>
@@ -6850,11 +6811,10 @@
         <v>203189</v>
       </c>
       <c r="E36" s="26">
-        <f t="shared" si="0"/>
         <v>0.81287640188792032</v>
       </c>
-      <c r="F36" s="34"/>
-      <c r="G36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="2" t="s">
         <v>79</v>
       </c>
@@ -6873,11 +6833,10 @@
         <v>278442</v>
       </c>
       <c r="E37" s="26">
-        <f t="shared" si="0"/>
         <v>0.37035961592409039</v>
       </c>
-      <c r="F37" s="35"/>
-      <c r="G37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="35"/>
       <c r="H37" s="2" t="s">
         <v>61</v>
       </c>
@@ -6896,13 +6855,12 @@
         <v>130595</v>
       </c>
       <c r="E38" s="26">
-        <f t="shared" si="0"/>
         <v>-0.53097952176754948</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="30">
         <v>1041784</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="33">
         <v>0.35737505846913153</v>
       </c>
       <c r="H38" s="2"/>
@@ -6921,11 +6879,10 @@
         <v>107489</v>
       </c>
       <c r="E39" s="26">
-        <f t="shared" si="0"/>
         <v>-0.17692867261380604</v>
       </c>
-      <c r="F39" s="34"/>
-      <c r="G39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="34"/>
       <c r="H39" s="2"/>
     </row>
     <row r="40" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6942,11 +6899,10 @@
         <v>390534</v>
       </c>
       <c r="E40" s="26">
-        <f t="shared" si="0"/>
         <v>2.6332461926336648</v>
       </c>
-      <c r="F40" s="34"/>
-      <c r="G40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="34"/>
       <c r="H40" s="2" t="s">
         <v>80</v>
       </c>
@@ -6965,11 +6921,10 @@
         <v>413166</v>
       </c>
       <c r="E41" s="26">
-        <f t="shared" si="0"/>
         <v>5.7951420362887737E-2</v>
       </c>
-      <c r="F41" s="35"/>
-      <c r="G41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="35"/>
       <c r="H41" s="2" t="s">
         <v>81</v>
       </c>
@@ -6988,13 +6943,12 @@
         <v>185591</v>
       </c>
       <c r="E42" s="26">
-        <f t="shared" si="0"/>
         <v>-0.55080766568401074</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="30">
         <v>797396</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="33">
         <v>-0.23458605622662662</v>
       </c>
       <c r="H42" s="2"/>
@@ -7013,11 +6967,10 @@
         <v>157238</v>
       </c>
       <c r="E43" s="26">
-        <f t="shared" si="0"/>
         <v>-0.15277141671740549</v>
       </c>
-      <c r="F43" s="34"/>
-      <c r="G43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="34"/>
       <c r="H43" s="2"/>
     </row>
     <row r="44" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7034,11 +6987,10 @@
         <v>180158</v>
       </c>
       <c r="E44" s="26">
-        <f t="shared" si="0"/>
         <v>0.14576629059133289</v>
       </c>
-      <c r="F44" s="34"/>
-      <c r="G44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="34"/>
       <c r="H44" s="2"/>
     </row>
     <row r="45" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7055,11 +7007,10 @@
         <v>274409</v>
       </c>
       <c r="E45" s="26">
-        <f t="shared" si="0"/>
         <v>0.523157450682179</v>
       </c>
-      <c r="F45" s="35"/>
-      <c r="G45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="35"/>
       <c r="H45" s="6" t="s">
         <v>24</v>
       </c>
@@ -7350,12 +7301,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="G6:G9"/>
     <mergeCell ref="F57:F60"/>
     <mergeCell ref="G57:G60"/>
     <mergeCell ref="G38:G41"/>
@@ -7368,6 +7313,12 @@
     <mergeCell ref="G48:G51"/>
     <mergeCell ref="F52:F55"/>
     <mergeCell ref="G52:G55"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G6:G9"/>
     <mergeCell ref="G14:G17"/>
     <mergeCell ref="G10:G13"/>
     <mergeCell ref="F14:F17"/>

--- a/data/CDPR_Revenue_Analysis.xlsx
+++ b/data/CDPR_Revenue_Analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tosie\Desktop\projekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tosie\Documents\GitHub\cdpr-data-analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4643F4-0EF1-43F4-9976-A4565A40FB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A040A42-FB77-4439-9B32-1929DA40BDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D18EEC2-743B-47E3-8CD0-9B3567279D3C}"/>
   </bookViews>
@@ -334,7 +334,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0.0%;\-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,33 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial CE"/>
       <charset val="238"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -403,9 +379,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -527,142 +510,139 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -822,7 +802,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6E908821-A8F4-4089-8CDA-052D23066816}" type="CELLRANGE">
+                    <a:fld id="{4A3B995C-EAEA-428F-A03C-41038028AD78}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -867,7 +847,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{CAB0A438-39BA-4B44-9DEE-E3BF12733334}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -929,7 +909,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{22C5607E-1960-4B7E-9442-59FA7631B6B8}" type="CELLRANGE">
+                    <a:fld id="{249A4790-0730-4183-BF43-A13FFB711F74}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -964,7 +944,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{14D95C14-36CC-4F5E-ABA0-81939D4A1DBC}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -997,7 +977,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{8B77BD92-0D90-445C-9FE9-11FA71819032}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -1075,7 +1055,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{A185950D-E25C-4F9E-A888-AF5631594C30}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -1108,7 +1088,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{1C9518BA-0E75-47F7-984B-9B1FF60233A8}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -1141,7 +1121,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{9E15197D-6BEC-4E7C-AAAE-5A3FA7819BAA}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -1173,7 +1153,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DAE46517-F15E-44D1-B760-0EA68A915B4A}" type="CELLRANGE">
+                    <a:fld id="{6A2BCF2D-5D6E-4321-88D0-935EE4828D56}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1773,7 +1753,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{298D9E95-1F7D-42E5-B1D4-EA90E5EB5927}" type="CELLRANGE">
+                    <a:fld id="{8AB21BFC-2447-4E66-941E-3DB6A4E95DFF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -1808,7 +1788,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{586C87E8-706A-42CA-859C-0008A8EB7951}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -1855,7 +1835,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{2BA197E6-76CB-4F0B-AF7D-2A80E35DF6C8}" type="CELLRANGE">
+                    <a:fld id="{076CA3C0-10FD-4272-ABC3-4F6F406A12CF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr>
                         <a:defRPr sz="1100" b="1">
@@ -1938,7 +1918,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{EAAD7C44-5BEE-4166-AD1E-DDB94433D9E6}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -1970,7 +1950,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C8CA119E-0D25-48E0-9579-8D24913E1BE3}" type="CELLRANGE">
+                    <a:fld id="{7CB6F364-CAFE-4391-8F69-02E3F842AB3C}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2005,7 +1985,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{3E0125E4-5914-4935-9245-B3889EAA1F1F}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -2038,7 +2018,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{A0873FC1-CFD4-4241-9E3D-DC9FF163E87D}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -2071,7 +2051,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{5264B0B2-BDB6-47A8-80D7-A1025DD9F9DD}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -2103,7 +2083,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E43A1127-276F-4A9F-975E-E1E385A9AF65}" type="CELLRANGE">
+                    <a:fld id="{30E39082-2D8D-4A8B-8ED0-9E91AA190DB7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -2138,7 +2118,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{414632CC-45EC-40C8-9A40-5B87446B6F69}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -2171,7 +2151,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{3051B2E5-B9D9-4A73-A7EA-3A1414D58D64}" type="CELLRANGE">
-                      <a:rPr lang="en-GB"/>
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
@@ -6019,1288 +5999,1302 @@
   <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="25" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="25" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="25" customWidth="1"/>
-    <col min="7" max="7" width="11" style="25" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" style="25" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="25" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="6" style="27" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="27" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="27" customWidth="1"/>
+    <col min="7" max="7" width="11" style="27" customWidth="1"/>
+    <col min="8" max="8" width="39.140625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="27" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="6">
         <v>2014</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="9">
         <v>4801</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="30">
+      <c r="E2" s="10"/>
+      <c r="F2" s="11">
         <v>21513</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="6"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="6">
         <v>2014</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="9">
         <v>7565</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="10">
         <v>0.57571339304311597</v>
       </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="6"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+      <c r="A4" s="6">
         <v>2014</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="9">
         <v>2775</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="10">
         <v>-0.63317911434236618</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="6"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="6">
         <v>2014</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="9">
         <v>6372</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="10">
         <v>1.2962162162162163</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="6"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="18">
         <v>2015</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="20">
         <v>2857</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="10">
         <v>-0.5516321406151915</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="11">
         <v>630856</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="21">
         <v>28.324408497187701</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="18">
         <v>2015</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="9">
         <v>406248</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="10">
         <v>141.19390969548476</v>
       </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="6" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+      <c r="A8" s="18">
         <v>2015</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="9">
         <v>85022</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="10">
         <v>-0.79071404659222932</v>
       </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="6"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="18">
         <v>2015</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="9">
         <v>136729</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="10">
         <v>0.60816024087883136</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="6" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
+      <c r="A10" s="18">
         <v>2016</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="9">
         <v>63667</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="10">
         <v>-0.53435628140335989</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="11">
         <v>438763</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="21">
         <v>-0.30449579618803657</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="A11" s="18">
         <v>2016</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="9">
         <v>175537</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="10">
         <v>1.7571112193129879</v>
       </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="6" t="s">
+      <c r="F11" s="14"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="13" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="A12" s="18">
         <v>2016</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="9">
         <v>72418</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="10">
         <v>-0.58744879996809785</v>
       </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="6"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
+      <c r="A13" s="18">
         <v>2016</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="9">
         <v>127141</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="10">
         <v>0.75565467149051346</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="6" t="s">
+      <c r="F13" s="16"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+      <c r="A14" s="18">
         <v>2017</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="9">
         <v>77710</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="10">
         <v>-0.38878882500530909</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="11">
         <v>346841</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="21">
         <v>-0.2095026244236638</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
+      <c r="A15" s="18">
         <v>2017</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="9">
         <v>121911</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="10">
         <v>0.56879423497619352</v>
       </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="6"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="A16" s="18">
         <v>2017</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="9">
         <v>59087</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="10">
         <v>-0.51532675476372103</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="6"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
+      <c r="A17" s="18">
         <v>2017</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="9">
         <v>88133</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="10">
         <v>0.49158021222942438</v>
       </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="6" t="s">
+      <c r="F17" s="16"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="A18" s="18">
         <v>2018</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="9">
         <v>52217</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="10">
         <v>-0.40752045204406978</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="11">
         <v>235919</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="21">
         <v>-0.31980648193264349</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
+      <c r="A19" s="18">
         <v>2018</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="9">
         <v>56555</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="10">
         <v>8.3076392745657548E-2</v>
       </c>
-      <c r="F19" s="31"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="6"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="6">
         <v>2018</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="9">
         <v>40675</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="10">
         <v>-0.28078861285474316</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="6"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+      <c r="A21" s="18">
         <v>2018</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="9">
         <v>86472</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="10">
         <v>1.1259250153657037</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="6"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="6">
         <v>2019</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="9">
         <v>50870</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="10">
         <v>-0.41171708761217501</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="11">
         <v>304475</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="21">
         <v>0.2905912622552656</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="6">
         <v>2019</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="9">
         <v>58905</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="10">
         <v>0.15795164143896206</v>
       </c>
-      <c r="F23" s="31"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="14" t="s">
+      <c r="F23" s="14"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="6">
         <v>2019</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="9">
         <v>47147</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="10">
         <v>-0.19960954078601137</v>
       </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="6"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="6">
         <v>2019</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="9">
         <v>147553</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="10">
         <v>2.1296370924979322</v>
       </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="6"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="13"/>
     </row>
     <row r="26" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="A26" s="18">
         <v>2020</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="9">
         <v>137220</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="10">
         <v>-7.0029074298726554E-2</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="11">
         <v>1839932</v>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="21">
         <v>5.0429657607356928</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
+      <c r="A27" s="18">
         <v>2020</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="9">
         <v>100445</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="10">
         <v>-0.26800029150269639</v>
       </c>
-      <c r="F27" s="31"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="6" t="s">
+      <c r="F27" s="14"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
+      <c r="A28" s="18">
         <v>2020</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="9">
         <v>61902</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="10">
         <v>-0.38372243516352234</v>
       </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="6" t="s">
+      <c r="F28" s="14"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
+      <c r="A29" s="18">
         <v>2020</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="25">
         <v>1540365</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="10">
         <v>23.883929436851798</v>
       </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="2" t="s">
+      <c r="F29" s="16"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="26" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
+      <c r="A30" s="18">
         <v>2021</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="25">
         <v>145868</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="10">
         <v>-0.90530296390790499</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="11">
         <v>691564</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="21">
         <v>-0.62413610937795527</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
+      <c r="A31" s="18">
         <v>2021</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="25">
         <v>221118</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="10">
         <v>0.51587736857981192</v>
       </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="2" t="s">
+      <c r="F31" s="14"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="26" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
+      <c r="A32" s="18">
         <v>2021</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="25">
         <v>104262</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="10">
         <v>-0.52847800721786553</v>
       </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="2" t="s">
+      <c r="F32" s="14"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="26" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
+      <c r="A33" s="18">
         <v>2021</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="25">
         <v>220316</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="10">
         <v>1.1130996911626478</v>
       </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="2"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
+      <c r="A34" s="18">
         <v>2022</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="25">
         <v>173787</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="10">
         <v>-0.21119210588427531</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="11">
         <v>767499</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="21">
         <v>0.10980184046595833</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="26" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
+      <c r="A35" s="18">
         <v>2022</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="25">
         <v>112081</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="10">
         <v>-0.35506683468844047</v>
       </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="2" t="s">
+      <c r="F35" s="14"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="26" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
+      <c r="A36" s="18">
         <v>2022</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="25">
         <v>203189</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="10">
         <v>0.81287640188792032</v>
       </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="2" t="s">
+      <c r="F36" s="14"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="26" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
+      <c r="A37" s="18">
         <v>2022</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="25">
         <v>278442</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="10">
         <v>0.37035961592409039</v>
       </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="2" t="s">
+      <c r="F37" s="16"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
+      <c r="A38" s="18">
         <v>2023</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="25">
         <v>130595</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="10">
         <v>-0.53097952176754948</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="11">
         <v>1041784</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="21">
         <v>0.35737505846913153</v>
       </c>
-      <c r="H38" s="2"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
+      <c r="A39" s="18">
         <v>2023</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="25">
         <v>107489</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="10">
         <v>-0.17692867261380604</v>
       </c>
-      <c r="F39" s="31"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="2"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
+      <c r="A40" s="18">
         <v>2023</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="25">
         <v>390534</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="10">
         <v>2.6332461926336648</v>
       </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="2" t="s">
+      <c r="F40" s="14"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="26" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
+      <c r="A41" s="18">
         <v>2023</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="25">
         <v>413166</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="10">
         <v>5.7951420362887737E-2</v>
       </c>
-      <c r="F41" s="32"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="2" t="s">
+      <c r="F41" s="16"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="26" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
+      <c r="A42" s="18">
         <v>2024</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="25">
         <v>185591</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="10">
         <v>-0.55080766568401074</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="11">
         <v>797396</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="21">
         <v>-0.23458605622662662</v>
       </c>
-      <c r="H42" s="2"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
+      <c r="A43" s="18">
         <v>2024</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="25">
         <v>157238</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="10">
         <v>-0.15277141671740549</v>
       </c>
-      <c r="F43" s="31"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="2"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="26"/>
     </row>
     <row r="44" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
+      <c r="A44" s="18">
         <v>2024</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="25">
         <v>180158</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="10">
         <v>0.14576629059133289</v>
       </c>
-      <c r="F44" s="31"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="2"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="26"/>
     </row>
     <row r="45" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
+      <c r="A45" s="6">
         <v>2024</v>
       </c>
-      <c r="B45" s="24" t="s">
+      <c r="B45" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="9">
         <v>274409</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="10">
         <v>0.523157450682179</v>
       </c>
-      <c r="F45" s="32"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="6" t="s">
+      <c r="F45" s="16"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+      <c r="A48" s="28">
         <v>2025</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="29">
         <v>179832</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="30">
         <v>-3.1030599544158929E-2</v>
       </c>
-      <c r="F48" s="39">
+      <c r="F48" s="31">
         <v>724803.4475924049</v>
       </c>
-      <c r="G48" s="42">
+      <c r="G48" s="32">
         <v>-9.1037015996562679E-2</v>
       </c>
-      <c r="H48" s="5"/>
+      <c r="H48" s="19"/>
     </row>
     <row r="49" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="21">
+      <c r="A49" s="33">
         <v>2025</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="36">
         <v>215752.12872392911</v>
       </c>
-      <c r="E49" s="28">
+      <c r="E49" s="37">
         <v>0.3610494961878527</v>
       </c>
-      <c r="F49" s="40"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="16"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="34"/>
     </row>
     <row r="50" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="21">
+      <c r="A50" s="33">
         <v>2025</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="36">
         <v>121531.06890325664</v>
       </c>
-      <c r="E50" s="28">
+      <c r="E50" s="37">
         <v>0.36100002675542653</v>
       </c>
-      <c r="F50" s="40"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="16"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="34"/>
     </row>
     <row r="51" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="21">
+      <c r="A51" s="33">
         <v>2025</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="D51" s="18">
+      <c r="D51" s="36">
         <v>207688.24996521923</v>
       </c>
-      <c r="E51" s="28">
+      <c r="E51" s="37">
         <v>-0.18170719056843873</v>
       </c>
-      <c r="F51" s="41"/>
-      <c r="G51" s="44"/>
-      <c r="H51" s="19"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="42"/>
     </row>
     <row r="52" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="29">
+      <c r="A52" s="43">
         <v>2026</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D52" s="18">
+      <c r="D52" s="36">
         <v>148430.38993153075</v>
       </c>
-      <c r="E52" s="28">
+      <c r="E52" s="37">
         <v>0.21185592994506547</v>
       </c>
-      <c r="F52" s="39">
+      <c r="F52" s="31">
         <v>653194.66418511141</v>
       </c>
-      <c r="G52" s="42">
+      <c r="G52" s="32">
         <v>-9.8797520410751238E-2</v>
       </c>
-      <c r="H52" s="16"/>
+      <c r="H52" s="34"/>
     </row>
     <row r="53" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="29">
+      <c r="A53" s="43">
         <v>2026</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="D53" s="18">
+      <c r="D53" s="36">
         <v>198087.63740002186</v>
       </c>
-      <c r="E53" s="28">
+      <c r="E53" s="37">
         <v>-7.5556123975874731E-2</v>
       </c>
-      <c r="F53" s="40"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="16"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="34"/>
     </row>
     <row r="54" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="29">
+      <c r="A54" s="43">
         <v>2026</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D54" s="18">
+      <c r="D54" s="36">
         <v>122713.79697460329</v>
       </c>
-      <c r="E54" s="28">
+      <c r="E54" s="37">
         <v>-0.21318964151211378</v>
       </c>
-      <c r="F54" s="40"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="16"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="34"/>
     </row>
     <row r="55" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="29">
+      <c r="A55" s="43">
         <v>2026</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="18">
+      <c r="D55" s="36">
         <v>183962.83987895545</v>
       </c>
-      <c r="E55" s="28">
+      <c r="E55" s="37">
         <v>-4.6530060564736131E-2</v>
       </c>
-      <c r="F55" s="41"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="16"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="34"/>
     </row>
     <row r="56" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="21">
+      <c r="A57" s="33">
         <v>2026</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D57" s="18">
+      <c r="D57" s="36">
         <v>155665.94480820085</v>
       </c>
-      <c r="E57" s="28">
+      <c r="E57" s="37">
         <v>-0.13438128470905708</v>
       </c>
-      <c r="F57" s="39">
+      <c r="F57" s="31">
         <v>1288316.1379912619</v>
       </c>
-      <c r="G57" s="42">
+      <c r="G57" s="32">
         <v>0.97233108080956543</v>
       </c>
-      <c r="H57" s="16"/>
+      <c r="H57" s="34"/>
     </row>
     <row r="58" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="21">
+      <c r="A58" s="33">
         <v>2026</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="D58" s="18">
+      <c r="D58" s="36">
         <v>755745.84061898128</v>
       </c>
-      <c r="E58" s="28">
+      <c r="E58" s="37">
         <v>2.502843031440094</v>
       </c>
-      <c r="F58" s="40"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="16" t="s">
+      <c r="F58" s="38"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="34" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="21">
+      <c r="A59" s="33">
         <v>2026</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="36">
         <v>139845.525722438</v>
       </c>
-      <c r="E59" s="28">
+      <c r="E59" s="37">
         <v>0.15069773502741254</v>
       </c>
-      <c r="F59" s="40"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="16"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="34"/>
     </row>
     <row r="60" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="21">
+      <c r="A60" s="33">
         <v>2026</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D60" s="18">
+      <c r="D60" s="36">
         <v>237058.82684164197</v>
       </c>
-      <c r="E60" s="28">
+      <c r="E60" s="37">
         <v>0.14141665155029867</v>
       </c>
-      <c r="F60" s="41"/>
-      <c r="G60" s="44"/>
-      <c r="H60" s="16"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="34"/>
     </row>
     <row r="61" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
+      <c r="A61" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="1" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G6:G9"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="F14:F17"/>
     <mergeCell ref="F57:F60"/>
     <mergeCell ref="G57:G60"/>
     <mergeCell ref="G38:G41"/>
@@ -7315,20 +7309,6 @@
     <mergeCell ref="G52:G55"/>
     <mergeCell ref="F42:F45"/>
     <mergeCell ref="G42:G45"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="G6:G9"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="G26:G29"/>
-    <mergeCell ref="G22:G25"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="G18:G21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
